--- a/Shareef/Suspension Tools/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2 - Test.xlsx
+++ b/Shareef/Suspension Tools/3D_Suspension_Analyzer/3D_Suspension_Analyzer_V2 - Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\share\OneDrive\Documents\Personal Projects\GOGO Kart\CAD\GOGO_KART_FSAE\Shareef\Suspension Tools\3D_Suspension_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DBD78C-914A-467D-903A-FC0135B077CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFC02A9-722A-4394-B6B9-645442FE515A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
+    <workbookView xWindow="-23148" yWindow="4152" windowWidth="23256" windowHeight="12456" xr2:uid="{9695B30A-B9BA-4C2C-80C9-40991A052BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="2" r:id="rId1"/>
@@ -818,127 +818,127 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="41"/>
                 <c:pt idx="0">
-                  <c:v>-4.481455409386534</c:v>
+                  <c:v>-2.0883551089184444</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4.5096282411695068</c:v>
+                  <c:v>-2.5763506707456134</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4.5337589113301595</c:v>
+                  <c:v>-3.0638600295437848</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.5539317551658343</c:v>
+                  <c:v>-3.5509636816380783</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-4.5702252042057925</c:v>
+                  <c:v>-4.0377436717552353</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-4.5827119694154002</c:v>
+                  <c:v>-4.5242836376833493</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-4.5914592125202569</c:v>
+                  <c:v>-5.0106688580265724</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-4.5965287054464969</c:v>
+                  <c:v>-5.4969863031953548</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.5979769778990534</c:v>
+                  <c:v>-5.9833246897785246</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-4.5958554531206639</c:v>
+                  <c:v>-6.4697745384524143</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-4.5902105718840218</c:v>
+                  <c:v>-6.9564282355886098</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-4.5810839047740481</c:v>
+                  <c:v>-7.4433800987328516</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-4.5685122528115603</c:v>
+                  <c:v>-7.9307264461353046</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-4.552527736461915</c:v>
+                  <c:v>-8.4185656705234386</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-4.533157873055548</c:v>
+                  <c:v>-8.906998317320193</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-4.5104256426280429</c:v>
+                  <c:v>-9.3961271675208771</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-4.4843495421615902</c:v>
+                  <c:v>-9.8860573254560595</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-4.4549436281809491</c:v>
+                  <c:v>-10.376896311680971</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-4.4222175476229966</c:v>
+                  <c:v>-10.868754161246352</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-4.3861765568610096</c:v>
+                  <c:v>-11.361743527622336</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-4.346821528722181</c:v>
+                  <c:v>-11.85597979256281</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-4.3041489472911785</c:v>
+                  <c:v>-12.35158118221694</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-4.258150890240632</c:v>
+                  <c:v>-12.848668889813315</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-4.2088149983734144</c:v>
+                  <c:v>-13.347367205263314</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-4.1561244320006185</c:v>
+                  <c:v>-13.847803652052725</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-4.1000578137126542</c:v>
+                  <c:v>-14.350109131814541</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-4.0405891570269974</c:v>
+                  <c:v>-14.854418077001696</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-3.9776877803165664</c:v>
+                  <c:v>-15.360868612105893</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-3.9113182053348545</c:v>
+                  <c:v>-15.86960272389795</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-3.8414400395590254</c:v>
+                  <c:v>-16.380766441197441</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-3.7680078414639691</c:v>
+                  <c:v>-16.894510024712048</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-3.6909709677256304</c:v>
+                  <c:v>-17.410988167524188</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-3.6102734012226483</c:v>
+                  <c:v>-17.930360206840753</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-3.5258535585610882</c:v>
+                  <c:v>-18.452790347663029</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-3.4376440756897959</c:v>
+                  <c:v>-18.978447899078734</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-3.3455715699963791</c:v>
+                  <c:v>-19.507507523925312</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-3.249556377075816</c:v>
+                  <c:v>-20.040149502623613</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-3.1495122601440277</c:v>
+                  <c:v>-20.576560012036865</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-3.0453460898189029</c:v>
+                  <c:v>-21.116931420266063</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-2.9369574917140335</c:v>
+                  <c:v>-21.661462598356255</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-2.8242384589742762</c:v>
+                  <c:v>-22.21035924995325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2400,34 +2400,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523DEDE4-CF63-4BE7-9597-216ED5BF300E}">
   <dimension ref="C3:AC46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="159" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="22.85546875" customWidth="1"/>
-    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
+    <col min="16" max="16" width="22.88671875" customWidth="1"/>
+    <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.109375" customWidth="1"/>
     <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="32.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C3" s="11" t="s">
         <v>82</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T4" s="8">
         <f>AC4-H4</f>
-        <v>-4.481455409386534</v>
+        <v>-2.0883551089184444</v>
       </c>
       <c r="U4" s="9">
         <f t="shared" ref="U4:U44" si="0">$D$5+$D$22*COS(RADIANS(S4))</f>
@@ -2524,30 +2524,30 @@
       </c>
       <c r="X4" s="9">
         <f>($D$23^2-$D$27^2+W4^2)/(2*W4)</f>
-        <v>115.32668853346802</v>
+        <v>61.434034014766787</v>
       </c>
       <c r="Y4" s="10">
         <f>SQRT($D$23^2-X4^2)</f>
-        <v>46.901544877588584</v>
+        <v>108.28600770493146</v>
       </c>
       <c r="Z4" s="9">
         <f>DEGREES(ATAN2(AA4-$D$7,AB4-$D$8))</f>
-        <v>19.027538152840954</v>
+        <v>-19.274066118437965</v>
       </c>
       <c r="AA4" s="9">
         <f>$D$7+X4*(U4-$D$7)/W4-$D$35*Y4*(V4-$D$8)/W4</f>
-        <v>197.69661835661304</v>
+        <v>197.52088404701223</v>
       </c>
       <c r="AB4" s="9">
         <f>$D$8+X4*(V4-$D$8)/W4+$D$35*Y4*(U4-$D$7)/W4</f>
-        <v>70.589481733791331</v>
+        <v>-11.095520592988095</v>
       </c>
       <c r="AC4" s="8">
         <f>-DEGREES(ATAN((U4-AA4)/(V4-AB4)))</f>
-        <v>-4.481455409386534</v>
+        <v>-2.0883551089184444</v>
       </c>
     </row>
-    <row r="5" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="T5" s="8">
         <f>AC5-H4</f>
-        <v>-4.5096282411695068</v>
+        <v>-2.5763506707456134</v>
       </c>
       <c r="U5" s="9">
         <f t="shared" si="0"/>
@@ -2581,30 +2581,30 @@
       </c>
       <c r="X5" s="9">
         <f t="shared" ref="X5:X44" si="3">($D$23^2-$D$27^2+W5^2)/(2*W5)</f>
-        <v>115.12289929027561</v>
+        <v>60.999577451726154</v>
       </c>
       <c r="Y5" s="10">
         <f t="shared" ref="Y5:Y44" si="4">SQRT($D$23^2-X5^2)</f>
-        <v>47.399557582334666</v>
+        <v>108.53133902569738</v>
       </c>
       <c r="Z5" s="9">
         <f t="shared" ref="Z5:Z44" si="5">DEGREES(ATAN2(AA5-$D$7,AB5-$D$8))</f>
-        <v>18.15372127701399</v>
+        <v>-20.129862661025609</v>
       </c>
       <c r="AA5" s="9">
         <f t="shared" ref="AA5:AA44" si="6">$D$7+X5*(U5-$D$7)/W5-$D$35*Y5*(V5-$D$8)/W5</f>
-        <v>198.30193639031026</v>
+        <v>196.89397587027489</v>
       </c>
       <c r="AB5" s="9">
         <f t="shared" ref="AB5:AB44" si="7">$D$8+X5*(V5-$D$8)/W5+$D$35*Y5*(U5-$D$7)/W5</f>
-        <v>68.78984205050314</v>
+        <v>-12.846218097278935</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" ref="AC5:AC44" si="8">-DEGREES(ATAN((U5-AA5)/(V5-AB5)))</f>
-        <v>-4.5096282411695068</v>
+        <v>-2.5763506707456134</v>
       </c>
     </row>
-    <row r="6" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="T6" s="8">
         <f>AC6-H4</f>
-        <v>-4.5337589113301595</v>
+        <v>-3.0638600295437848</v>
       </c>
       <c r="U6" s="9">
         <f t="shared" si="0"/>
@@ -2638,30 +2638,30 @@
       </c>
       <c r="X6" s="9">
         <f t="shared" si="3"/>
-        <v>114.91698767726145</v>
+        <v>60.557125010406786</v>
       </c>
       <c r="Y6" s="10">
         <f t="shared" si="4"/>
-        <v>47.896617241556235</v>
+        <v>108.77883346715005</v>
       </c>
       <c r="Z6" s="9">
         <f t="shared" si="5"/>
-        <v>17.27884422564712</v>
+        <v>-20.990448702449068</v>
       </c>
       <c r="AA6" s="9">
         <f t="shared" si="6"/>
-        <v>198.88042308444278</v>
+        <v>196.23726178350708</v>
       </c>
       <c r="AB6" s="9">
         <f t="shared" si="7"/>
-        <v>66.97898061417979</v>
+        <v>-14.597073593145609</v>
       </c>
       <c r="AC6" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5337589113301595</v>
+        <v>-3.0638600295437848</v>
       </c>
     </row>
-    <row r="7" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="T7" s="8">
         <f>AC7-H4</f>
-        <v>-4.5539317551658343</v>
+        <v>-3.5509636816380783</v>
       </c>
       <c r="U7" s="9">
         <f t="shared" si="0"/>
@@ -2695,30 +2695,30 @@
       </c>
       <c r="X7" s="9">
         <f t="shared" si="3"/>
-        <v>114.70905247509666</v>
+        <v>60.106668904948251</v>
       </c>
       <c r="Y7" s="10">
         <f t="shared" si="4"/>
-        <v>48.392491982388364</v>
+        <v>109.02838324560686</v>
       </c>
       <c r="Z7" s="9">
         <f t="shared" si="5"/>
-        <v>16.402985706360017</v>
+        <v>-21.855839679194951</v>
       </c>
       <c r="AA7" s="9">
         <f t="shared" si="6"/>
-        <v>199.43179475277836</v>
+        <v>195.55043841783657</v>
       </c>
       <c r="AB7" s="9">
         <f t="shared" si="7"/>
-        <v>65.157451587540137</v>
+        <v>-16.347558527345925</v>
       </c>
       <c r="AC7" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5539317551658343</v>
+        <v>-3.5509636816380783</v>
       </c>
     </row>
-    <row r="8" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T8" s="8">
         <f>AC8-H4</f>
-        <v>-4.5702252042057925</v>
+        <v>-4.0377436717552353</v>
       </c>
       <c r="U8" s="9">
         <f t="shared" si="0"/>
@@ -2752,30 +2752,30 @@
       </c>
       <c r="X8" s="9">
         <f t="shared" si="3"/>
-        <v>114.49919537347066</v>
+        <v>59.648200593953923</v>
       </c>
       <c r="Y8" s="10">
         <f t="shared" si="4"/>
-        <v>48.88695387143482</v>
+        <v>109.27987996837952</v>
       </c>
       <c r="Z8" s="9">
         <f t="shared" si="5"/>
-        <v>15.526222402889298</v>
+        <v>-22.726052448670984</v>
       </c>
       <c r="AA8" s="9">
         <f t="shared" si="6"/>
-        <v>199.9557843498585</v>
+        <v>194.83320794677309</v>
       </c>
       <c r="AB8" s="9">
         <f t="shared" si="7"/>
-        <v>63.325812833451621</v>
+        <v>-18.097134557613444</v>
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5702252042057925</v>
+        <v>-4.0377436717552353</v>
       </c>
     </row>
-    <row r="9" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C9" s="2" t="s">
         <v>30</v>
       </c>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="T9" s="8">
         <f>AC9-H4</f>
-        <v>-4.5827119694154002</v>
+        <v>-4.5242836376833493</v>
       </c>
       <c r="U9" s="9">
         <f t="shared" si="0"/>
@@ -2809,30 +2809,30 @@
       </c>
       <c r="X9" s="9">
         <f t="shared" si="3"/>
-        <v>114.28752105299905</v>
+        <v>59.181710737396948</v>
       </c>
       <c r="Y9" s="10">
         <f t="shared" si="4"/>
-        <v>49.379778569372895</v>
+        <v>109.53321466201508</v>
       </c>
       <c r="Z9" s="9">
         <f t="shared" si="5"/>
-        <v>14.648629120573638</v>
+        <v>-23.601105360796655</v>
       </c>
       <c r="AA9" s="9">
         <f t="shared" si="6"/>
-        <v>200.45214130636751</v>
+        <v>194.08527818124935</v>
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="7"/>
-        <v>61.48462568795884</v>
+        <v>-19.845253558457856</v>
       </c>
       <c r="AC9" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5827119694154002</v>
+        <v>-4.5242836376833493</v>
       </c>
     </row>
-    <row r="10" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T10" s="8">
         <f>AC10-H4</f>
-        <v>-4.5914592125202569</v>
+        <v>-5.0106688580265724</v>
       </c>
       <c r="U10" s="9">
         <f t="shared" si="0"/>
@@ -2866,35 +2866,35 @@
       </c>
       <c r="X10" s="9">
         <f t="shared" si="3"/>
-        <v>114.07413727089647</v>
+        <v>58.707189151671024</v>
       </c>
       <c r="Y10" s="10">
         <f t="shared" si="4"/>
-        <v>49.870744990431696</v>
+        <v>109.78827779826916</v>
       </c>
       <c r="Z10" s="9">
         <f t="shared" si="5"/>
-        <v>13.770278928452155</v>
+        <v>-24.481018331530898</v>
       </c>
       <c r="AA10" s="9">
         <f t="shared" si="6"/>
-        <v>200.92063137563241</v>
+        <v>193.3063626579964</v>
       </c>
       <c r="AB10" s="9">
         <f t="shared" si="7"/>
-        <v>59.634454739684642</v>
+        <v>-21.591357621355556</v>
       </c>
       <c r="AC10" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5914592125202569</v>
+        <v>-5.0106688580265724</v>
       </c>
     </row>
-    <row r="11" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="2">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>21</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="T11" s="8">
         <f>AC11-H4</f>
-        <v>-4.5965287054464969</v>
+        <v>-5.4969863031953548</v>
       </c>
       <c r="U11" s="9">
         <f t="shared" si="0"/>
@@ -2923,30 +2923,30 @@
       </c>
       <c r="X11" s="9">
         <f t="shared" si="3"/>
-        <v>113.85915495059858</v>
+        <v>58.224624762701687</v>
       </c>
       <c r="Y11" s="10">
         <f t="shared" si="4"/>
-        <v>50.359634966266221</v>
+        <v>110.04495931773789</v>
       </c>
       <c r="Z11" s="9">
         <f t="shared" si="5"/>
-        <v>12.891243298134027</v>
+        <v>-25.365812918463863</v>
       </c>
       <c r="AA11" s="9">
         <f t="shared" si="6"/>
-        <v>201.36103649125238</v>
+        <v>192.49618072123445</v>
       </c>
       <c r="AB11" s="9">
         <f t="shared" si="7"/>
-        <v>57.775867615052285</v>
+        <v>-23.334879048661563</v>
       </c>
       <c r="AC11" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5965287054464969</v>
+        <v>-5.4969863031953548</v>
       </c>
     </row>
-    <row r="12" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="T12" s="8">
         <f>AC12-H4</f>
-        <v>-4.5979769778990534</v>
+        <v>-5.9833246897785246</v>
       </c>
       <c r="U12" s="9">
         <f t="shared" si="0"/>
@@ -2980,30 +2980,30 @@
       </c>
       <c r="X12" s="9">
         <f t="shared" si="3"/>
-        <v>113.64268827552598</v>
+        <v>57.734005557028127</v>
       </c>
       <c r="Y12" s="10">
         <f t="shared" si="4"/>
-        <v>50.84623291367442</v>
+        <v>110.30314865107454</v>
       </c>
       <c r="Z12" s="9">
         <f t="shared" si="5"/>
-        <v>12.011592239625786</v>
+        <v>-26.255512398608399</v>
       </c>
       <c r="AA12" s="9">
         <f t="shared" si="6"/>
-        <v>201.77315463582019</v>
+        <v>191.65445759767584</v>
       </c>
       <c r="AB12" s="9">
         <f t="shared" si="7"/>
-        <v>55.909434768837123</v>
+        <v>-25.075240340545193</v>
       </c>
       <c r="AC12" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5979769778990534</v>
+        <v>-5.9833246897785246</v>
       </c>
     </row>
-    <row r="13" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="T13" s="8">
         <f>AC13-H4</f>
-        <v>-4.5958554531206639</v>
+        <v>-6.4697745384524143</v>
       </c>
       <c r="U13" s="9">
         <f t="shared" si="0"/>
@@ -3037,30 +3037,30 @@
       </c>
       <c r="X13" s="9">
         <f t="shared" si="3"/>
-        <v>113.42485478719375</v>
+        <v>57.235318530761859</v>
       </c>
       <c r="Y13" s="10">
         <f t="shared" si="4"/>
-        <v>51.330325505533381</v>
+        <v>110.56273473771454</v>
       </c>
       <c r="Z13" s="9">
         <f t="shared" si="5"/>
-        <v>11.131394434329703</v>
+        <v>-27.150141848536283</v>
       </c>
       <c r="AA13" s="9">
         <f t="shared" si="6"/>
-        <v>202.15679972067437</v>
+        <v>190.78092446485093</v>
       </c>
       <c r="AB13" s="9">
         <f t="shared" si="7"/>
-        <v>54.035729279617215</v>
+        <v>-26.811854174221374</v>
       </c>
       <c r="AC13" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5958554531206639</v>
+        <v>-6.4697745384524143</v>
       </c>
     </row>
-    <row r="14" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="T14" s="8">
         <f>AC14-H4</f>
-        <v>-4.5902105718840218</v>
+        <v>-6.9564282355886098</v>
       </c>
       <c r="U14" s="9">
         <f t="shared" si="0"/>
@@ -3094,30 +3094,30 @@
       </c>
       <c r="X14" s="9">
         <f t="shared" si="3"/>
-        <v>113.20577548788178</v>
+        <v>56.728549636322299</v>
       </c>
       <c r="Y14" s="10">
         <f t="shared" si="4"/>
-        <v>51.811701344264925</v>
+        <v>110.82360604203113</v>
       </c>
       <c r="Z14" s="9">
         <f t="shared" si="5"/>
-        <v>10.250717365450708</v>
+        <v>-28.049728227013613</v>
       </c>
       <c r="AA14" s="9">
         <f t="shared" si="6"/>
-        <v>202.51180147660429</v>
+        <v>189.87531851278473</v>
       </c>
       <c r="AB14" s="9">
         <f t="shared" si="7"/>
-        <v>52.155326649749526</v>
+        <v>-28.544123374717174</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5902105718840218</v>
+        <v>-6.9564282355886098</v>
       </c>
     </row>
-    <row r="15" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="T15" s="8">
         <f>AC15-H4</f>
-        <v>-4.5810839047740481</v>
+        <v>-7.4433800987328516</v>
       </c>
       <c r="U15" s="9">
         <f t="shared" si="0"/>
@@ -3151,30 +3151,30 @@
       </c>
       <c r="X15" s="9">
         <f t="shared" si="3"/>
-        <v>112.98557494809292</v>
+        <v>56.21368372684573</v>
       </c>
       <c r="Y15" s="10">
         <f t="shared" si="4"/>
-        <v>52.29015063708345</v>
+        <v>111.08565056684036</v>
       </c>
       <c r="Z15" s="9">
         <f t="shared" si="5"/>
-        <v>9.3696274460685736</v>
+        <v>-28.954300460299994</v>
       </c>
       <c r="AA15" s="9">
         <f t="shared" si="6"/>
-        <v>202.83800535542721</v>
+        <v>188.93738299906704</v>
       </c>
       <c r="AB15" s="9">
         <f t="shared" si="7"/>
-        <v>50.268804609547999</v>
+        <v>-30.271440876376793</v>
       </c>
       <c r="AC15" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5810839047740481</v>
+        <v>-7.4433800987328516</v>
       </c>
     </row>
-    <row r="16" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T16" s="8">
         <f>AC16-H4</f>
-        <v>-4.5685122528115603</v>
+        <v>-7.9307264461353046</v>
       </c>
       <c r="U16" s="9">
         <f t="shared" si="0"/>
@@ -3208,36 +3208,36 @@
       </c>
       <c r="X16" s="9">
         <f t="shared" si="3"/>
-        <v>112.76438141903819</v>
+        <v>55.690704498157004</v>
       </c>
       <c r="Y16" s="10">
         <f t="shared" si="4"/>
-        <v>52.765464872221827</v>
+        <v>111.34875586417189</v>
       </c>
       <c r="Z16" s="9">
         <f t="shared" si="5"/>
-        <v>8.4881901451512096</v>
+        <v>-29.863889530287</v>
       </c>
       <c r="AA16" s="9">
         <f t="shared" si="6"/>
-        <v>203.13527244235962</v>
+        <v>187.966867297378</v>
       </c>
       <c r="AB16" s="9">
         <f t="shared" si="7"/>
-        <v>48.376742925389841</v>
+        <v>-31.993189674272784</v>
       </c>
       <c r="AC16" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5685122528115603</v>
+        <v>-7.9307264461353046</v>
       </c>
     </row>
-    <row r="17" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="S17" s="6">
         <v>7</v>
       </c>
       <c r="T17" s="8">
         <f>AC17-H4</f>
-        <v>-4.552527736461915</v>
+        <v>-8.4185656705234386</v>
       </c>
       <c r="U17" s="9">
         <f t="shared" si="0"/>
@@ -3253,30 +3253,30 @@
       </c>
       <c r="X17" s="9">
         <f t="shared" si="3"/>
-        <v>112.5423269504022</v>
+        <v>55.159594428188484</v>
       </c>
       <c r="Y17" s="10">
         <f t="shared" si="4"/>
-        <v>53.237436495278153</v>
+        <v>111.61280904321761</v>
       </c>
       <c r="Z17" s="9">
         <f t="shared" si="5"/>
-        <v>7.6064701118015599</v>
+        <v>-30.778528565662146</v>
       </c>
       <c r="AA17" s="9">
         <f t="shared" si="6"/>
-        <v>203.40347937911491</v>
+        <v>186.96352693954964</v>
       </c>
       <c r="AB17" s="9">
         <f t="shared" si="7"/>
-        <v>46.479723211521438</v>
+        <v>-33.70874276464923</v>
       </c>
       <c r="AC17" s="8">
         <f t="shared" si="8"/>
-        <v>-4.552527736461915</v>
+        <v>-8.4185656705234386</v>
       </c>
     </row>
-    <row r="18" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C18" s="12" t="s">
         <v>6</v>
       </c>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="T18" s="8">
         <f>AC18-H4</f>
-        <v>-4.533157873055548</v>
+        <v>-8.906998317320193</v>
       </c>
       <c r="U18" s="9">
         <f t="shared" si="0"/>
@@ -3304,30 +3304,30 @@
       </c>
       <c r="X18" s="9">
         <f t="shared" si="3"/>
-        <v>112.31954751365511</v>
+        <v>54.620334713724652</v>
       </c>
       <c r="Y18" s="10">
         <f t="shared" si="4"/>
-        <v>53.705858584774269</v>
+        <v>111.87769677536576</v>
       </c>
       <c r="Z18" s="9">
         <f t="shared" si="5"/>
-        <v>6.7245312980453704</v>
+        <v>-31.698252936296722</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="6"/>
-        <v>203.64251829767838</v>
+        <v>185.92712365126266</v>
       </c>
       <c r="AB18" s="9">
         <f t="shared" si="7"/>
-        <v>44.578328745376176</v>
+        <v>-35.417463073479901</v>
       </c>
       <c r="AC18" s="8">
         <f t="shared" si="8"/>
-        <v>-4.533157873055548</v>
+        <v>-8.906998317320193</v>
       </c>
     </row>
-    <row r="19" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="T19" s="8">
         <f>AC19-H4</f>
-        <v>-4.5104256426280429</v>
+        <v>-9.3961271675208771</v>
       </c>
       <c r="U19" s="9">
         <f t="shared" si="0"/>
@@ -3361,30 +3361,30 @@
       </c>
       <c r="X19" s="9">
         <f t="shared" si="3"/>
-        <v>112.09618313119336</v>
+        <v>54.072905204343591</v>
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="4"/>
-        <v>54.170524525963032</v>
+        <v>112.14330529622386</v>
       </c>
       <c r="Z19" s="9">
         <f t="shared" si="5"/>
-        <v>5.8424370804836787</v>
+        <v>-32.623100351068516</v>
       </c>
       <c r="AA19" s="9">
         <f t="shared" si="6"/>
-        <v>203.85229676473358</v>
+        <v>184.85742538150242</v>
       </c>
       <c r="AB19" s="9">
         <f t="shared" si="7"/>
-        <v>42.673144286260168</v>
+        <v>-37.118703372179709</v>
       </c>
       <c r="AC19" s="8">
         <f t="shared" si="8"/>
-        <v>-4.5104256426280429</v>
+        <v>-9.3961271675208771</v>
       </c>
     </row>
-    <row r="20" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="T20" s="8">
         <f>AC20-H4</f>
-        <v>-4.4843495421615902</v>
+        <v>-9.8860573254560595</v>
       </c>
       <c r="U20" s="9">
         <f t="shared" si="0"/>
@@ -3419,30 +3419,30 @@
       </c>
       <c r="X20" s="9">
         <f t="shared" si="3"/>
-        <v>111.8723780116059</v>
+        <v>53.517284333420754</v>
       </c>
       <c r="Y20" s="10">
         <f t="shared" si="4"/>
-        <v>54.631227681870342</v>
+        <v>112.40952040452711</v>
       </c>
       <c r="Z20" s="9">
         <f t="shared" si="5"/>
-        <v>4.9602503811467935</v>
+        <v>-33.553110959342888</v>
       </c>
       <c r="AA20" s="9">
         <f t="shared" si="6"/>
-        <v>204.03273773674283</v>
+        <v>183.75420632591798</v>
       </c>
       <c r="AB20" s="9">
         <f t="shared" si="7"/>
-        <v>40.764755897296055</v>
+        <v>-38.811806179454692</v>
       </c>
       <c r="AC20" s="8">
         <f t="shared" si="8"/>
-        <v>-4.4843495421615902</v>
+        <v>-9.8860573254560595</v>
       </c>
     </row>
-    <row r="21" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C21" s="2" t="s">
         <v>43</v>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="T21" s="8">
         <f>AC21-H4</f>
-        <v>-4.4549436281809491</v>
+        <v>-10.376896311680971</v>
       </c>
       <c r="U21" s="9">
         <f t="shared" si="0"/>
@@ -3477,30 +3477,30 @@
       </c>
       <c r="X21" s="9">
         <f t="shared" si="3"/>
-        <v>111.64828069138034</v>
+        <v>52.95344904605291</v>
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="4"/>
-        <v>55.087761060500078</v>
+        <v>112.67622745782306</v>
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="5"/>
-        <v>4.078033787902517</v>
+        <v>-34.488327456350319</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="6"/>
-        <v>204.18377952572109</v>
+        <v>182.61724694425698</v>
       </c>
       <c r="AB21" s="9">
         <f t="shared" si="7"/>
-        <v>38.853750770554271</v>
+        <v>-40.496103648225699</v>
       </c>
       <c r="AC21" s="8">
         <f t="shared" si="8"/>
-        <v>-4.4549436281809491</v>
+        <v>-10.376896311680971</v>
       </c>
     </row>
-    <row r="22" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C22" s="2" t="s">
         <v>12</v>
       </c>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="T22" s="8">
         <f>AC22-H4</f>
-        <v>-4.4222175476229966</v>
+        <v>-10.868754161246352</v>
       </c>
       <c r="U22" s="9">
         <f t="shared" si="0"/>
@@ -3535,30 +3535,30 @@
       </c>
       <c r="X22" s="9">
         <f t="shared" si="3"/>
-        <v>111.42404418338035</v>
+        <v>52.381374723752508</v>
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="4"/>
-        <v>55.539916977072494</v>
+        <v>112.94331136481621</v>
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="5"/>
-        <v>3.1958496747870471</v>
+        <v>-35.428795192712997</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="6"/>
-        <v>204.30537577577954</v>
+        <v>181.44633397207468</v>
       </c>
       <c r="AB22" s="9">
         <f t="shared" si="7"/>
-        <v>36.940717055336805</v>
+        <v>-42.170917436501327</v>
       </c>
       <c r="AC22" s="8">
         <f t="shared" si="8"/>
-        <v>-4.4222175476229966</v>
+        <v>-10.868754161246352</v>
       </c>
     </row>
-    <row r="23" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C23" s="2" t="s">
         <v>13</v>
       </c>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="T23" s="8">
         <f>AC23-H4</f>
-        <v>-4.3861765568610096</v>
+        <v>-11.361743527622336</v>
       </c>
       <c r="U23" s="9">
         <f t="shared" si="0"/>
@@ -3593,30 +3593,30 @@
       </c>
       <c r="X23" s="9">
         <f t="shared" si="3"/>
-        <v>111.19982613244392</v>
+        <v>51.801035105755403</v>
       </c>
       <c r="Y23" s="10">
         <f t="shared" si="4"/>
-        <v>55.987486710105522</v>
+        <v>113.21065657424789</v>
       </c>
       <c r="Z23" s="9">
         <f t="shared" si="5"/>
-        <v>2.3137603226416652</v>
+        <v>-36.37456228838866</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="6"/>
-        <v>204.39749545056227</v>
+        <v>180.24126042694687</v>
       </c>
       <c r="AB23" s="9">
         <f t="shared" si="7"/>
-        <v>35.026243689609601</v>
+        <v>-43.835558561014629</v>
       </c>
       <c r="AC23" s="8">
         <f t="shared" si="8"/>
-        <v>-4.3861765568610096</v>
+        <v>-11.361743527622336</v>
       </c>
     </row>
-    <row r="24" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C24" s="2" t="s">
         <v>14</v>
       </c>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="T24" s="8">
         <f>AC24-H4</f>
-        <v>-4.346821528722181</v>
+        <v>-11.85597979256281</v>
       </c>
       <c r="U24" s="9">
         <f t="shared" si="0"/>
@@ -3651,30 +3651,30 @@
       </c>
       <c r="X24" s="9">
         <f t="shared" si="3"/>
-        <v>110.97578897847251</v>
+        <v>51.212402206776225</v>
       </c>
       <c r="Y24" s="10">
         <f t="shared" si="4"/>
-        <v>56.430260150078524</v>
+        <v>113.47814706017799</v>
       </c>
       <c r="Z24" s="9">
         <f t="shared" si="5"/>
-        <v>1.4318280404579051</v>
+        <v>-37.325679751316315</v>
       </c>
       <c r="AA24" s="9">
         <f t="shared" si="6"/>
-        <v>204.46012283174818</v>
+        <v>179.00182560944992</v>
       </c>
       <c r="AB24" s="9">
         <f t="shared" si="7"/>
-        <v>33.110920234617922</v>
+        <v>-45.489327232371515</v>
       </c>
       <c r="AC24" s="8">
         <f t="shared" si="8"/>
-        <v>-4.346821528722181</v>
+        <v>-11.85597979256281</v>
       </c>
     </row>
-    <row r="25" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C25" s="2" t="s">
         <v>15</v>
       </c>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="T25" s="8">
         <f>AC25-H4</f>
-        <v>-4.3041489472911785</v>
+        <v>-12.35158118221694</v>
       </c>
       <c r="U25" s="9">
         <f t="shared" si="0"/>
@@ -3709,30 +3709,30 @@
       </c>
       <c r="X25" s="9">
         <f t="shared" si="3"/>
-        <v>110.75210012740075</v>
+        <v>50.615446231037623</v>
       </c>
       <c r="Y25" s="10">
         <f t="shared" si="4"/>
-        <v>56.86802543934683</v>
+        <v>113.74566630352534</v>
       </c>
       <c r="Z25" s="9">
         <f t="shared" si="5"/>
-        <v>0.5501152878514004</v>
+        <v>-38.28220160106634</v>
       </c>
       <c r="AA25" s="9">
         <f t="shared" si="6"/>
-        <v>204.49325752884434</v>
+        <v>177.72783509920754</v>
       </c>
       <c r="AB25" s="9">
         <f t="shared" si="7"/>
-        <v>31.195336712749189</v>
+        <v>-47.131512670387181</v>
       </c>
       <c r="AC25" s="8">
         <f t="shared" si="8"/>
-        <v>-4.3041489472911785</v>
+        <v>-12.35158118221694</v>
       </c>
     </row>
-    <row r="26" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C26" s="2" t="s">
         <v>26</v>
       </c>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T26" s="8">
         <f>AC26-H4</f>
-        <v>-4.258150890240632</v>
+        <v>-12.848668889813315</v>
       </c>
       <c r="U26" s="9">
         <f t="shared" si="0"/>
@@ -3767,36 +3767,36 @@
       </c>
       <c r="X26" s="9">
         <f t="shared" si="3"/>
-        <v>110.52893213045891</v>
+        <v>50.010135482390147</v>
       </c>
       <c r="Y26" s="10">
         <f t="shared" si="4"/>
-        <v>57.300568601894412</v>
+        <v>114.01309726971276</v>
       </c>
       <c r="Z26" s="9">
         <f t="shared" si="5"/>
-        <v>-0.33131520089371436</v>
+        <v>-39.244184997816227</v>
       </c>
       <c r="AA26" s="9">
         <f t="shared" si="6"/>
-        <v>204.49691450055795</v>
+        <v>176.41910074634438</v>
       </c>
       <c r="AB26" s="9">
         <f t="shared" si="7"/>
-        <v>29.280083448743021</v>
+        <v>-48.761392898210566</v>
       </c>
       <c r="AC26" s="8">
         <f t="shared" si="8"/>
-        <v>-4.258150890240632</v>
+        <v>-12.848668889813315</v>
       </c>
     </row>
-    <row r="27" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="2">
         <f>SQRT((D11^2)-(D26^2))</f>
-        <v>67.082039324993687</v>
+        <v>148.66068747318505</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>21</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T27" s="8">
         <f>AC27-H4</f>
-        <v>-4.2088149983734144</v>
+        <v>-13.347367205263314</v>
       </c>
       <c r="U27" s="9">
         <f t="shared" si="0"/>
@@ -3826,30 +3826,30 @@
       </c>
       <c r="X27" s="9">
         <f t="shared" si="3"/>
-        <v>110.30646287216263</v>
+        <v>49.396436270330447</v>
       </c>
       <c r="Y27" s="10">
         <f t="shared" si="4"/>
-        <v>57.727673161424136</v>
+        <v>114.28032238225084</v>
       </c>
       <c r="Z27" s="9">
         <f t="shared" si="5"/>
-        <v>-1.2124002907446598</v>
+        <v>-40.211690376992443</v>
       </c>
       <c r="AA27" s="9">
         <f t="shared" si="6"/>
-        <v>204.47112408809895</v>
+        <v>175.07544065873196</v>
       </c>
       <c r="AB27" s="9">
         <f t="shared" si="7"/>
-        <v>27.365750914382552</v>
+        <v>-50.378234513753391</v>
       </c>
       <c r="AC27" s="8">
         <f t="shared" si="8"/>
-        <v>-4.2088149983734144</v>
+        <v>-13.347367205263314</v>
       </c>
     </row>
-    <row r="28" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C28" s="2" t="s">
         <v>50</v>
       </c>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="T28" s="8">
         <f>AC28-H4</f>
-        <v>-4.1561244320006185</v>
+        <v>-13.847803652052725</v>
       </c>
       <c r="U28" s="9">
         <f t="shared" si="0"/>
@@ -3884,30 +3884,30 @@
       </c>
       <c r="X28" s="9">
         <f t="shared" si="3"/>
-        <v>110.08487576748935</v>
+        <v>48.774312811715689</v>
       </c>
       <c r="Y28" s="10">
         <f t="shared" si="4"/>
-        <v>58.14911974618736</v>
+        <v>114.54722349208167</v>
       </c>
       <c r="Z28" s="9">
         <f t="shared" si="5"/>
-        <v>-2.093076317312963</v>
+        <v>-41.184781589941153</v>
       </c>
       <c r="AA28" s="9">
         <f t="shared" si="6"/>
-        <v>204.41593206083689</v>
+        <v>173.69667918546125</v>
       </c>
       <c r="AB28" s="9">
         <f t="shared" si="7"/>
-        <v>25.452929576836333</v>
+        <v>-51.981292436852598</v>
       </c>
       <c r="AC28" s="8">
         <f t="shared" si="8"/>
-        <v>-4.1561244320006185</v>
+        <v>-13.847803652052725</v>
       </c>
     </row>
-    <row r="29" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="T29" s="8">
         <f>AC29-H4</f>
-        <v>-4.1000578137126542</v>
+        <v>-14.350109131814541</v>
       </c>
       <c r="U29" s="9">
         <f t="shared" si="0"/>
@@ -3942,30 +3942,30 @@
       </c>
       <c r="X29" s="9">
         <f t="shared" si="3"/>
-        <v>109.86435996872575</v>
+        <v>48.143727127961917</v>
       </c>
       <c r="Y29" s="10">
         <f t="shared" si="4"/>
-        <v>58.56468567884788</v>
+        <v>114.81368184248925</v>
       </c>
       <c r="Z29" s="9">
         <f t="shared" si="5"/>
-        <v>-2.9732789552005254</v>
+        <v>-42.1635260510118</v>
       </c>
       <c r="AA29" s="9">
         <f t="shared" si="6"/>
-        <v>204.3313996748129</v>
+        <v>172.28264689703195</v>
       </c>
       <c r="AB29" s="9">
         <f t="shared" si="7"/>
-        <v>23.54220975085628</v>
+        <v>-53.569809630498241</v>
       </c>
       <c r="AC29" s="8">
         <f t="shared" si="8"/>
-        <v>-4.1000578137126542</v>
+        <v>-14.350109131814541</v>
       </c>
     </row>
-    <row r="30" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C30" s="4" t="s">
         <v>54</v>
       </c>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="T30" s="8">
         <f>AC30-H4</f>
-        <v>-4.0405891570269974</v>
+        <v>-14.854418077001696</v>
       </c>
       <c r="U30" s="9">
         <f t="shared" si="0"/>
@@ -4000,36 +4000,36 @@
       </c>
       <c r="X30" s="9">
         <f t="shared" si="3"/>
-        <v>109.64511058249774</v>
+        <v>47.504638937503486</v>
       </c>
       <c r="Y30" s="10">
         <f t="shared" si="4"/>
-        <v>58.974144549555291</v>
+        <v>115.07957802936814</v>
       </c>
       <c r="Z30" s="9">
         <f t="shared" si="5"/>
-        <v>-3.852943082745548</v>
+        <v>-43.147994891462574</v>
       </c>
       <c r="AA30" s="9">
         <f t="shared" si="6"/>
-        <v>204.21760374469244</v>
+        <v>170.83318056280876</v>
       </c>
       <c r="AB30" s="9">
         <f t="shared" si="7"/>
-        <v>21.634181455077218</v>
+        <v>-55.143016794357152</v>
       </c>
       <c r="AC30" s="8">
         <f t="shared" si="8"/>
-        <v>-4.0405891570269974</v>
+        <v>-14.854418077001696</v>
       </c>
     </row>
-    <row r="31" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C31" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="5">
         <f>(D23^2 - D27^2 + D30^2)/(2*D30)</f>
-        <v>110.97578897847251</v>
+        <v>51.212402206776225</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>21</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="T31" s="8">
         <f>AC31-H4</f>
-        <v>-3.9776877803165664</v>
+        <v>-15.360868612105893</v>
       </c>
       <c r="U31" s="9">
         <f t="shared" si="0"/>
@@ -4058,36 +4058,36 @@
       </c>
       <c r="X31" s="9">
         <f t="shared" si="3"/>
-        <v>109.4273288975225</v>
+        <v>46.857005543279584</v>
       </c>
       <c r="Y31" s="10">
         <f t="shared" si="4"/>
-        <v>59.377265770271343</v>
+        <v>115.34479195662483</v>
       </c>
       <c r="Z31" s="9">
         <f t="shared" si="5"/>
-        <v>-4.7320026425792179</v>
+        <v>-44.138263120621765</v>
       </c>
       <c r="AA31" s="9">
         <f t="shared" si="6"/>
-        <v>204.07463672983801</v>
+        <v>169.34812312636376</v>
       </c>
       <c r="AB31" s="9">
         <f t="shared" si="7"/>
-        <v>19.729434272702754</v>
+        <v>-56.700132028712282</v>
       </c>
       <c r="AC31" s="8">
         <f t="shared" si="8"/>
-        <v>-3.9776877803165664</v>
+        <v>-15.360868612105893</v>
       </c>
     </row>
-    <row r="32" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C32" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="5">
         <f>SQRT(D23^2 - D31^2)</f>
-        <v>56.430260150078524</v>
+        <v>113.47814706017799</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>21</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="T32" s="8">
         <f>AC32-H4</f>
-        <v>-3.9113182053348545</v>
+        <v>-15.86960272389795</v>
       </c>
       <c r="U32" s="9">
         <f t="shared" si="0"/>
@@ -4116,36 +4116,36 @@
       </c>
       <c r="X32" s="9">
         <f t="shared" si="3"/>
-        <v>109.21122262365213</v>
+        <v>46.200781715002378</v>
       </c>
       <c r="Y32" s="10">
         <f t="shared" si="4"/>
-        <v>59.773814108245531</v>
+        <v>115.60920278646809</v>
       </c>
       <c r="Z32" s="9">
         <f t="shared" si="5"/>
-        <v>-5.6103904973618848</v>
+        <v>-45.134409794766398</v>
       </c>
       <c r="AA32" s="9">
         <f t="shared" si="6"/>
-        <v>203.90260683527981</v>
+        <v>167.82732367939892</v>
       </c>
       <c r="AB32" s="9">
         <f t="shared" si="7"/>
-        <v>17.828557216908401</v>
+        <v>-58.240360466818665</v>
       </c>
       <c r="AC32" s="8">
         <f t="shared" si="8"/>
-        <v>-3.9113182053348545</v>
+        <v>-15.86960272389795</v>
       </c>
     </row>
-    <row r="33" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C33" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D33" s="5">
         <f>D7 + D31*(D28-D7)/D30</f>
-        <v>177.63370892170718</v>
+        <v>125.05538384780229</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>21</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="T33" s="8">
         <f>AC33-H4</f>
-        <v>-3.8414400395590254</v>
+        <v>-16.380766441197441</v>
       </c>
       <c r="U33" s="9">
         <f t="shared" si="0"/>
@@ -4174,36 +4174,36 @@
       </c>
       <c r="X33" s="9">
         <f t="shared" si="3"/>
-        <v>108.9970061428093</v>
+        <v>45.535919565950529</v>
       </c>
       <c r="Y33" s="10">
         <f t="shared" si="4"/>
-        <v>60.16354919637299</v>
+        <v>115.87268888432375</v>
       </c>
       <c r="Z33" s="9">
         <f t="shared" si="5"/>
-        <v>-6.4880382800219376</v>
+        <v>-46.136518194208463</v>
       </c>
       <c r="AA33" s="9">
         <f t="shared" si="6"/>
-        <v>203.70163812847451</v>
+        <v>166.27063743502731</v>
       </c>
       <c r="AB33" s="9">
         <f t="shared" si="7"/>
-        <v>15.932138601338643</v>
+        <v>-59.762893873549245</v>
       </c>
       <c r="AC33" s="8">
         <f t="shared" si="8"/>
-        <v>-3.8414400395590254</v>
+        <v>-16.380766441197441</v>
       </c>
     </row>
-    <row r="34" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C34" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D34" s="5">
         <f>D8 + D31*(D29-D8)/D30</f>
-        <v>82.756844310343411</v>
+        <v>54.345893413793952</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>21</v>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="T34" s="8">
         <f>AC34-H4</f>
-        <v>-3.7680078414639691</v>
+        <v>-16.894510024712048</v>
       </c>
       <c r="U34" s="9">
         <f t="shared" si="0"/>
@@ -4232,30 +4232,30 @@
       </c>
       <c r="X34" s="9">
         <f t="shared" si="3"/>
-        <v>108.78490077244794</v>
+        <v>44.862368424017994</v>
       </c>
       <c r="Y34" s="10">
         <f t="shared" si="4"/>
-        <v>60.546225017986515</v>
+        <v>116.13512775808908</v>
       </c>
       <c r="Z34" s="9">
         <f t="shared" si="5"/>
-        <v>-7.3648762377676062</v>
+        <v>-47.144676009110199</v>
       </c>
       <c r="AA34" s="9">
         <f t="shared" si="6"/>
-        <v>203.47187067286291</v>
+        <v>164.67792570128535</v>
       </c>
       <c r="AB34" s="9">
         <f t="shared" si="7"/>
-        <v>14.040765916128201</v>
+        <v>-61.266910208068268</v>
       </c>
       <c r="AC34" s="8">
         <f t="shared" si="8"/>
-        <v>-3.7680078414639691</v>
+        <v>-16.894510024712048</v>
       </c>
     </row>
-    <row r="35" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C35" s="4" t="s">
         <v>64</v>
       </c>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="T35" s="8">
         <f>AC35-H4</f>
-        <v>-3.6909709677256304</v>
+        <v>-17.410988167524188</v>
       </c>
       <c r="U35" s="9">
         <f t="shared" si="0"/>
@@ -4289,36 +4289,36 @@
       </c>
       <c r="X35" s="9">
         <f t="shared" si="3"/>
-        <v>108.57513504220677</v>
+        <v>44.18007469673703</v>
       </c>
       <c r="Y35" s="10">
         <f t="shared" si="4"/>
-        <v>60.921589363431444</v>
+        <v>116.39639599141692</v>
       </c>
       <c r="Z35" s="9">
         <f t="shared" si="5"/>
-        <v>-8.2408330690834983</v>
+        <v>-48.158975534582972</v>
       </c>
       <c r="AA35" s="9">
         <f t="shared" si="6"/>
-        <v>203.21346067937091</v>
+        <v>163.04905585585325</v>
       </c>
       <c r="AB35" s="9">
         <f t="shared" si="7"/>
-        <v>12.155025709933952</v>
+        <v>-62.7515731481217</v>
       </c>
       <c r="AC35" s="8">
         <f t="shared" si="8"/>
-        <v>-3.6909709677256304</v>
+        <v>-17.410988167524188</v>
       </c>
     </row>
-    <row r="36" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C36" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D36" s="1">
         <f>D33 - D35*D32*(D29-D8)/D30</f>
-        <v>204.46012283174818</v>
+        <v>179.00182560944992</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>21</v>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="T36" s="8">
         <f>AC36-H4</f>
-        <v>-3.6102734012226483</v>
+        <v>-17.930360206840753</v>
       </c>
       <c r="U36" s="9">
         <f t="shared" si="0"/>
@@ -4347,36 +4347,36 @@
       </c>
       <c r="X36" s="9">
         <f t="shared" si="3"/>
-        <v>108.36794498445839</v>
+        <v>43.488981729981404</v>
       </c>
       <c r="Y36" s="10">
         <f t="shared" si="4"/>
-        <v>61.289383255547605</v>
+        <v>116.65636917069442</v>
       </c>
       <c r="Z36" s="9">
         <f t="shared" si="5"/>
-        <v>-9.1158357528572029</v>
+        <v>-49.179513875658984</v>
       </c>
       <c r="AA36" s="9">
         <f t="shared" si="6"/>
-        <v>202.92658067714413</v>
+        <v>161.38390132307802</v>
       </c>
       <c r="AB36" s="9">
         <f t="shared" si="7"/>
-        <v>10.275503478527696</v>
+        <v>-64.216031573376611</v>
       </c>
       <c r="AC36" s="8">
         <f t="shared" si="8"/>
-        <v>-3.6102734012226483</v>
+        <v>-17.930360206840753</v>
       </c>
     </row>
-    <row r="37" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C37" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D37" s="1">
         <f>D34 + D35*D32*(D28-D7)/D30</f>
-        <v>33.110920234617922</v>
+        <v>-45.489327232371515</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>21</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="T37" s="8">
         <f>AC37-H4</f>
-        <v>-3.5258535585610882</v>
+        <v>-18.452790347663029</v>
       </c>
       <c r="U37" s="9">
         <f t="shared" si="0"/>
@@ -4405,36 +4405,36 @@
       </c>
       <c r="X37" s="9">
         <f t="shared" si="3"/>
-        <v>108.16357443949472</v>
+        <v>42.789029660041919</v>
       </c>
       <c r="Y37" s="10">
         <f t="shared" si="4"/>
-        <v>61.649340340930515</v>
+        <v>116.91492180535406</v>
       </c>
       <c r="Z37" s="9">
         <f t="shared" si="5"/>
-        <v>-9.9898093687065366</v>
+        <v>-50.20639316276349</v>
       </c>
       <c r="AA37" s="9">
         <f t="shared" si="6"/>
-        <v>202.61141970497042</v>
+        <v>159.68234155452382</v>
       </c>
       <c r="AB37" s="9">
         <f t="shared" si="7"/>
-        <v>8.4027835605697732</v>
+        <v>-65.659419005073417</v>
       </c>
       <c r="AC37" s="8">
         <f t="shared" si="8"/>
-        <v>-3.5258535585610882</v>
+        <v>-18.452790347663029</v>
       </c>
     </row>
-    <row r="38" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="1">
         <f>DEGREES(ATAN2(D36-D7, D37-D8))</f>
-        <v>1.4318280404579051</v>
+        <v>-37.325679751316315</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>1</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="T38" s="8">
         <f>AC38-H4</f>
-        <v>-3.4376440756897959</v>
+        <v>-18.978447899078734</v>
       </c>
       <c r="U38" s="9">
         <f t="shared" si="0"/>
@@ -4463,36 +4463,36 @@
       </c>
       <c r="X38" s="9">
         <f t="shared" si="3"/>
-        <v>107.96227537612799</v>
+        <v>42.08015525875453</v>
       </c>
       <c r="Y38" s="10">
         <f t="shared" si="4"/>
-        <v>62.001186243563978</v>
+        <v>117.1719272411234</v>
       </c>
       <c r="Z38" s="9">
         <f t="shared" si="5"/>
-        <v>-10.862676907493782</v>
+        <v>-51.239720778354481</v>
       </c>
       <c r="AA38" s="9">
         <f t="shared" si="6"/>
-        <v>202.26818352502269</v>
+        <v>157.94426201442076</v>
       </c>
       <c r="AB38" s="9">
         <f t="shared" si="7"/>
-        <v>6.5374490412622421</v>
+        <v>-67.080852999071482</v>
       </c>
       <c r="AC38" s="8">
         <f t="shared" si="8"/>
-        <v>-3.4376440756897959</v>
+        <v>-18.978447899078734</v>
       </c>
     </row>
-    <row r="39" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="S39" s="6">
         <v>-15</v>
       </c>
       <c r="T39" s="8">
         <f>AC39-H4</f>
-        <v>-3.3455715699963791</v>
+        <v>-19.507507523925312</v>
       </c>
       <c r="U39" s="9">
         <f t="shared" si="0"/>
@@ -4508,30 +4508,30 @@
       </c>
       <c r="X39" s="9">
         <f t="shared" si="3"/>
-        <v>107.76430822852706</v>
+        <v>41.362291771347884</v>
       </c>
       <c r="Y39" s="10">
         <f t="shared" si="4"/>
-        <v>62.344637877102272</v>
+        <v>117.42725756578788</v>
       </c>
       <c r="Z39" s="9">
         <f t="shared" si="5"/>
-        <v>-11.734359070917828</v>
+        <v>-52.279609595440142</v>
       </c>
       <c r="AA39" s="9">
         <f t="shared" si="6"/>
-        <v>201.89709486075594</v>
+        <v>156.16955417154651</v>
       </c>
       <c r="AB39" s="9">
         <f t="shared" si="7"/>
-        <v>4.6800816646683501</v>
+        <v>-68.479434489175674</v>
       </c>
       <c r="AC39" s="8">
         <f t="shared" si="8"/>
-        <v>-3.3455715699963791</v>
+        <v>-19.507507523925312</v>
       </c>
     </row>
-    <row r="40" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C40" s="15" t="s">
         <v>7</v>
       </c>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="T40" s="8">
         <f>AC40-H4</f>
-        <v>-3.249556377075816</v>
+        <v>-20.040149502623613</v>
       </c>
       <c r="U40" s="9">
         <f t="shared" si="0"/>
@@ -4559,30 +4559,30 @@
       </c>
       <c r="X40" s="9">
         <f t="shared" si="3"/>
-        <v>107.56994225015053</v>
+        <v>40.635368746663012</v>
       </c>
       <c r="Y40" s="10">
         <f t="shared" si="4"/>
-        <v>62.679402711730425</v>
+        <v>117.68078350700561</v>
       </c>
       <c r="Z40" s="9">
         <f t="shared" si="5"/>
-        <v>-12.604774058967857</v>
+        <v>-53.326178228729695</v>
       </c>
       <c r="AA40" s="9">
         <f t="shared" si="6"/>
-        <v>201.4983936610127</v>
+        <v>154.35811549925847</v>
       </c>
       <c r="AB40" s="9">
         <f t="shared" si="7"/>
-        <v>2.8312617555840944</v>
+        <v>-69.854247077422485</v>
       </c>
       <c r="AC40" s="8">
         <f t="shared" si="8"/>
-        <v>-3.249556377075816</v>
+        <v>-20.040149502623613</v>
       </c>
     </row>
-    <row r="41" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C41" s="2" t="s">
         <v>3</v>
       </c>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="T41" s="8">
         <f>AC41-H4</f>
-        <v>-3.1495122601440277</v>
+        <v>-20.576560012036865</v>
       </c>
       <c r="U41" s="9">
         <f t="shared" si="0"/>
@@ -4616,36 +4616,36 @@
       </c>
       <c r="X41" s="9">
         <f t="shared" si="3"/>
-        <v>107.37945588568131</v>
+        <v>39.899311859387062</v>
       </c>
       <c r="Y41" s="10">
         <f t="shared" si="4"/>
-        <v>63.005177991138332</v>
+        <v>117.93237432167375</v>
       </c>
       <c r="Z41" s="9">
         <f t="shared" si="5"/>
-        <v>-13.473837343900618</v>
+        <v>-54.37955129922203</v>
       </c>
       <c r="AA41" s="9">
         <f t="shared" si="6"/>
-        <v>201.07233739264137</v>
+        <v>152.50984948559793</v>
       </c>
       <c r="AB41" s="9">
         <f t="shared" si="7"/>
-        <v>0.99156815195936332</v>
+        <v>-71.204356267780952</v>
       </c>
       <c r="AC41" s="8">
         <f t="shared" si="8"/>
-        <v>-3.1495122601440277</v>
+        <v>-20.576560012036865</v>
       </c>
     </row>
-    <row r="42" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C42" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D42" s="2">
         <f>DEGREES(ATAN(D26/(D29-D37)))</f>
-        <v>16.646794696917905</v>
+        <v>7.8272280346744791</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>1</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="T42" s="8">
         <f>AC42-H4</f>
-        <v>-3.0453460898189029</v>
+        <v>-21.116931420266063</v>
       </c>
       <c r="U42" s="9">
         <f t="shared" si="0"/>
@@ -4674,36 +4674,36 @@
       </c>
       <c r="X42" s="9">
         <f t="shared" si="3"/>
-        <v>107.19313716191166</v>
+        <v>39.154042723928335</v>
       </c>
       <c r="Y42" s="10">
         <f t="shared" si="4"/>
-        <v>63.321649894704983</v>
+        <v>118.18189767630572</v>
       </c>
       <c r="Z42" s="9">
         <f t="shared" si="5"/>
-        <v>-14.341461429265133</v>
+        <v>-55.43985971308836</v>
       </c>
       <c r="AA42" s="9">
         <f t="shared" si="6"/>
-        <v>200.61920136420832</v>
+        <v>150.62466565561755</v>
       </c>
       <c r="AB42" s="9">
         <f t="shared" si="7"/>
-        <v>-0.83842185100537847</v>
+        <v>-72.528808639485504</v>
       </c>
       <c r="AC42" s="8">
         <f t="shared" si="8"/>
-        <v>-3.0453460898189029</v>
+        <v>-21.116931420266063</v>
       </c>
     </row>
-    <row r="43" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C43" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D43" s="2">
         <f>-DEGREES(ATAN((D28 - D36)/(D29-D37)))</f>
-        <v>-4.346821528722181</v>
+        <v>-11.85597979256281</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>1</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="T43" s="8">
         <f>AC43-H4</f>
-        <v>-2.9369574917140335</v>
+        <v>-21.661462598356255</v>
       </c>
       <c r="U43" s="9">
         <f t="shared" si="0"/>
@@ -4732,36 +4732,36 @@
       </c>
       <c r="X43" s="9">
         <f t="shared" si="3"/>
-        <v>107.01128409857317</v>
+        <v>38.399478699549775</v>
       </c>
       <c r="Y43" s="10">
         <f t="shared" si="4"/>
-        <v>63.628492639496507</v>
+        <v>118.42921951783192</v>
       </c>
       <c r="Z43" s="9">
         <f t="shared" si="5"/>
-        <v>-15.207555592343695</v>
+        <v>-56.507240955760146</v>
       </c>
       <c r="AA43" s="9">
         <f t="shared" si="6"/>
-        <v>200.13927908369681</v>
+        <v>148.70247960834027</v>
       </c>
       <c r="AB43" s="9">
         <f t="shared" si="7"/>
-        <v>-2.6581325438183896</v>
+        <v>-73.826630955962287</v>
       </c>
       <c r="AC43" s="8">
         <f t="shared" si="8"/>
-        <v>-2.9369574917140335</v>
+        <v>-21.661462598356255</v>
       </c>
     </row>
-    <row r="44" spans="3:29" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:29" ht="15" x14ac:dyDescent="0.35">
       <c r="C44" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D44" s="1">
         <f>(D28-D5)*(D37-D8)-(D29-D6)*(D36-D7)</f>
-        <v>340.78423741989997</v>
+        <v>-8269.4414752117846</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>21</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="T44" s="8">
         <f>AC44-H4</f>
-        <v>-2.8242384589742762</v>
+        <v>-22.21035924995325</v>
       </c>
       <c r="U44" s="9">
         <f t="shared" si="0"/>
@@ -4790,36 +4790,36 @@
       </c>
       <c r="X44" s="9">
         <f t="shared" si="3"/>
-        <v>106.83420514015212</v>
+        <v>37.635532686365707</v>
       </c>
       <c r="Y44" s="10">
         <f t="shared" si="4"/>
-        <v>63.925367516126919</v>
+        <v>118.67420393418908</v>
       </c>
       <c r="Z44" s="9">
         <f t="shared" si="5"/>
-        <v>-16.072025608199755</v>
+        <v>-57.581839402193012</v>
       </c>
       <c r="AA44" s="9">
         <f t="shared" si="6"/>
-        <v>199.63288265343573</v>
+        <v>146.74321307104432</v>
       </c>
       <c r="AB44" s="9">
         <f t="shared" si="7"/>
-        <v>-4.4669898312758534</v>
+        <v>-75.096829205039171</v>
       </c>
       <c r="AC44" s="8">
         <f t="shared" si="8"/>
-        <v>-2.8242384589742762</v>
+        <v>-22.21035924995325</v>
       </c>
     </row>
-    <row r="45" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C45" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D45" s="1">
         <f>D5 + (((D7-D5)*(D37-D8)-(D8-D6)*(D36-D7))/D44)*(D28-D5)</f>
-        <v>2880.5245847431356</v>
+        <v>-11.802749431441484</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>21</v>
@@ -4828,7 +4828,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="3:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C46" s="2" t="s">
         <v>78</v>
       </c>
